--- a/src/width_txt/Разрядность_элементов_фильтра_Гилберта_задержки_АЦП_№1.xlsx
+++ b/src/width_txt/Разрядность_элементов_фильтра_Гилберта_задержки_АЦП_№1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="608" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="912" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -310,7 +310,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
@@ -321,7 +321,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="0">
         <v>1</v>
@@ -332,10 +332,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -343,10 +343,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -354,10 +354,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="0">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -365,10 +365,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
+        <v>34</v>
+      </c>
+      <c r="C7" s="0">
         <v>35</v>
-      </c>
-      <c r="C7" s="0">
-        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -376,10 +376,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="0">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -387,10 +387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" s="0">
         <v>36</v>
-      </c>
-      <c r="C9" s="0">
-        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -398,10 +398,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -409,10 +409,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
+        <v>36</v>
+      </c>
+      <c r="C11" s="0">
         <v>37</v>
-      </c>
-      <c r="C11" s="0">
-        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -420,10 +420,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="0">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -431,10 +431,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
+        <v>37</v>
+      </c>
+      <c r="C13" s="0">
         <v>38</v>
-      </c>
-      <c r="C13" s="0">
-        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -442,10 +442,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -453,10 +453,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
+        <v>38</v>
+      </c>
+      <c r="C15" s="0">
         <v>39</v>
-      </c>
-      <c r="C15" s="0">
-        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -464,10 +464,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -475,10 +475,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -486,10 +486,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -497,10 +497,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
+        <v>39</v>
+      </c>
+      <c r="C19" s="0">
         <v>40</v>
-      </c>
-      <c r="C19" s="0">
-        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -508,10 +508,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -519,10 +519,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -530,10 +530,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -541,10 +541,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
+        <v>40</v>
+      </c>
+      <c r="C23" s="0">
         <v>41</v>
-      </c>
-      <c r="C23" s="0">
-        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -552,10 +552,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
@@ -563,10 +563,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
@@ -574,10 +574,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -585,7 +585,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="0">
         <v>43</v>
@@ -596,7 +596,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="0">
         <v>43</v>
@@ -607,10 +607,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -618,10 +618,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -629,7 +629,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="0">
         <v>44</v>
@@ -640,7 +640,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="0">
         <v>44</v>
@@ -651,10 +651,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
@@ -662,10 +662,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -673,7 +673,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="0">
         <v>45</v>
@@ -684,10 +684,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C36" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -695,10 +695,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
@@ -706,10 +706,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -717,10 +717,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -728,10 +728,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
@@ -739,10 +739,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
@@ -750,10 +750,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -761,10 +761,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -772,10 +772,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
@@ -783,10 +783,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
@@ -794,10 +794,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -805,10 +805,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -816,10 +816,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C48" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
@@ -827,10 +827,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -838,10 +838,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C50" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -849,10 +849,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -860,10 +860,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -871,10 +871,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -882,10 +882,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -893,10 +893,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C55" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
@@ -904,10 +904,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
@@ -915,10 +915,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -926,10 +926,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59">
@@ -937,10 +937,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C59" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
@@ -948,10 +948,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
@@ -959,10 +959,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C61" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -970,10 +970,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
@@ -981,10 +981,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
@@ -992,10 +992,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C64" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65">
@@ -1003,10 +1003,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
@@ -1014,10 +1014,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
@@ -1025,10 +1025,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68">
@@ -1036,10 +1036,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C68" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
@@ -1047,10 +1047,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C69" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
@@ -1058,10 +1058,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
@@ -1069,10 +1069,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C71" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
@@ -1080,10 +1080,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C72" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
@@ -1091,10 +1091,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C73" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
@@ -1102,7 +1102,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="0">
         <v>0</v>
